--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -10,7 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPS" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strokes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akasia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,179 +448,179 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167</v>
+        <v>218</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mika Moerat</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>154</v>
+        <v>210</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85</v>
+        <v>164</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -625,10 +630,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -638,10 +643,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -651,10 +656,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -664,10 +669,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -677,10 +682,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -690,10 +695,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -703,10 +708,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -716,10 +721,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -729,10 +734,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -742,10 +747,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -755,10 +760,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -768,10 +773,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -781,10 +786,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>-6</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="3">
@@ -838,10 +843,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>-96</v>
       </c>
     </row>
     <row r="4">
@@ -851,101 +856,101 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>-31</v>
+        <v>-78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>-21</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>-12</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="12">
@@ -955,36 +960,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>-8</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>-6</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>-62</v>
       </c>
     </row>
     <row r="15">
@@ -994,10 +999,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="16">
@@ -1007,36 +1012,36 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -1046,10 +1051,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20">
@@ -1059,10 +1064,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>-55</v>
+        <v>-110</v>
       </c>
     </row>
     <row r="21">
@@ -1072,10 +1077,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="22">
@@ -1085,10 +1090,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>-41</v>
+        <v>-82</v>
       </c>
     </row>
     <row r="23">
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>-9</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="24">
@@ -1111,10 +1116,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>-56</v>
+        <v>-112</v>
       </c>
     </row>
     <row r="25">
@@ -1124,10 +1129,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
@@ -1137,10 +1142,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>74</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27">
@@ -1150,10 +1155,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1180,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,20 +1211,28 @@
           <t>Fairway Fighters</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
       <c r="C2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -1228,20 +1241,28 @@
           <t>Tee Tigers</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
       <c r="C4" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
       <c r="C5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6">
@@ -1250,9 +1271,388 @@
           <t>Birdie Buddies</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
       <c r="C6" t="n">
-        <v>103</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1266,9 +1666,3936 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>88</v>
+      </c>
+      <c r="C3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>91</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>86</v>
+      </c>
+      <c r="C5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>96</v>
+      </c>
+      <c r="C7" t="n">
+        <v>35</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C8" t="n">
+        <v>35</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>97</v>
+      </c>
+      <c r="C10" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>87</v>
+      </c>
+      <c r="C11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>92</v>
+      </c>
+      <c r="C12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>102</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>92</v>
+      </c>
+      <c r="C15" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>96</v>
+      </c>
+      <c r="C16" t="n">
+        <v>28</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>103</v>
+      </c>
+      <c r="C17" t="n">
+        <v>28</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>98</v>
+      </c>
+      <c r="C18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Brian Plaatjies</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>105</v>
+      </c>
+      <c r="C19" t="n">
+        <v>24</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>98</v>
+      </c>
+      <c r="C20" t="n">
+        <v>24</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>99</v>
+      </c>
+      <c r="C21" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lenny Booysen</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>112</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>112</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>90</v>
+      </c>
+      <c r="C25" t="n">
+        <v>40</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>88</v>
+      </c>
+      <c r="C26" t="n">
+        <v>36</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>91</v>
+      </c>
+      <c r="C27" t="n">
+        <v>36</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>86</v>
+      </c>
+      <c r="C28" t="n">
+        <v>36</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>93</v>
+      </c>
+      <c r="C29" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>96</v>
+      </c>
+      <c r="C30" t="n">
+        <v>35</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>89</v>
+      </c>
+      <c r="C31" t="n">
+        <v>35</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>93</v>
+      </c>
+      <c r="C32" t="n">
+        <v>34</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>97</v>
+      </c>
+      <c r="C33" t="n">
+        <v>33</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>87</v>
+      </c>
+      <c r="C34" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>92</v>
+      </c>
+      <c r="C35" t="n">
+        <v>32</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>99</v>
+      </c>
+      <c r="C36" t="n">
+        <v>31</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>102</v>
+      </c>
+      <c r="C37" t="n">
+        <v>30</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>92</v>
+      </c>
+      <c r="C38" t="n">
+        <v>29</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>96</v>
+      </c>
+      <c r="C39" t="n">
+        <v>28</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>103</v>
+      </c>
+      <c r="C40" t="n">
+        <v>28</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>98</v>
+      </c>
+      <c r="C41" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Brian Plaatjies</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>105</v>
+      </c>
+      <c r="C42" t="n">
+        <v>24</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>98</v>
+      </c>
+      <c r="C43" t="n">
+        <v>24</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>99</v>
+      </c>
+      <c r="C44" t="n">
+        <v>19</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Lenny Booysen</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>112</v>
+      </c>
+      <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>112</v>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>85</v>
+      </c>
+      <c r="C3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88</v>
+      </c>
+      <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>94</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>99</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>87</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>93</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>90</v>
+      </c>
+      <c r="C11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>96</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>110</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>80</v>
+      </c>
+      <c r="C17" t="n">
+        <v>38</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>85</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>88</v>
+      </c>
+      <c r="C19" t="n">
+        <v>34</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>79</v>
+      </c>
+      <c r="C20" t="n">
+        <v>32</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>94</v>
+      </c>
+      <c r="C21" t="n">
+        <v>32</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>99</v>
+      </c>
+      <c r="C22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>112</v>
+      </c>
+      <c r="C23" t="n">
+        <v>30</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>87</v>
+      </c>
+      <c r="C24" t="n">
+        <v>28</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>93</v>
+      </c>
+      <c r="C25" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>90</v>
+      </c>
+      <c r="C26" t="n">
+        <v>25</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>96</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>104</v>
+      </c>
+      <c r="C28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>100</v>
+      </c>
+      <c r="C29" t="n">
+        <v>24</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>110</v>
+      </c>
+      <c r="C30" t="n">
+        <v>18</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>102</v>
+      </c>
+      <c r="C31" t="n">
+        <v>16</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>94</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>99</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>83</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>93</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>94</v>
+      </c>
+      <c r="C19" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>90</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>93</v>
+      </c>
+      <c r="C21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>95</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>99</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>94</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>104</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>87</v>
+      </c>
+      <c r="C2" t="n">
+        <v>35</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>87</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>91</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>82</v>
+      </c>
+      <c r="C8" t="n">
+        <v>31</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lenny Booysen</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>93</v>
+      </c>
+      <c r="C11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>28</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>95</v>
+      </c>
+      <c r="C13" t="n">
+        <v>27</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>27</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>101</v>
+      </c>
+      <c r="C15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>115</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>108</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kirsten Jacobs</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>103</v>
+      </c>
+      <c r="C20" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>87</v>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>90</v>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>81</v>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>87</v>
+      </c>
+      <c r="C28" t="n">
+        <v>32</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>96</v>
+      </c>
+      <c r="C29" t="n">
+        <v>32</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>91</v>
+      </c>
+      <c r="C30" t="n">
+        <v>31</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>82</v>
+      </c>
+      <c r="C31" t="n">
+        <v>31</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Lenny Booysen</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>106</v>
+      </c>
+      <c r="C32" t="n">
+        <v>30</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>95</v>
+      </c>
+      <c r="C33" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>93</v>
+      </c>
+      <c r="C34" t="n">
+        <v>29</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>94</v>
+      </c>
+      <c r="C35" t="n">
+        <v>28</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>95</v>
+      </c>
+      <c r="C36" t="n">
+        <v>27</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" t="n">
+        <v>27</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>101</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>102</v>
+      </c>
+      <c r="C39" t="n">
+        <v>23</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" t="n">
+        <v>22</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>115</v>
+      </c>
+      <c r="C41" t="n">
+        <v>22</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>108</v>
+      </c>
+      <c r="C42" t="n">
+        <v>20</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kirsten Jacobs</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>103</v>
+      </c>
+      <c r="C43" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>94</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>99</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>90</v>
+      </c>
+      <c r="C14" t="n">
+        <v>37</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>83</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>93</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C17" t="n">
+        <v>35</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>93</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>94</v>
+      </c>
+      <c r="C19" t="n">
+        <v>31</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>90</v>
+      </c>
+      <c r="C20" t="n">
+        <v>29</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>93</v>
+      </c>
+      <c r="C21" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>95</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>99</v>
+      </c>
+      <c r="C23" t="n">
+        <v>27</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>94</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>104</v>
+      </c>
+      <c r="C25" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,36 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Akasia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Sheet2</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Rounds_Played</t>
         </is>
       </c>
@@ -444,105 +474,211 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arno Adonis</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>28</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Arno Adonis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>218</v>
+        <v>176</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="D3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>37</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>210</v>
+        <v>106</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>34</v>
+      </c>
+      <c r="F5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Brian Plaatjies</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>206</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mika Moerat</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>29</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>28</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
-      </c>
-      <c r="C8" t="n">
-        <v>12</v>
+        <v>109</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>37</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>27</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -552,244 +688,500 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>172</v>
+        <v>86</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>24</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>31</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>34</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>166</v>
+        <v>51</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>27</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="D15" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Kirsten Jacobs</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>162</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>19</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>35</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="D20" t="n">
+        <v>28</v>
+      </c>
+      <c r="E20" t="n">
+        <v>29</v>
+      </c>
+      <c r="F20" t="n">
+        <v>35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>29</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="D21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>29</v>
+      </c>
+      <c r="F22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>29</v>
+      </c>
+      <c r="I22" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>90</v>
-      </c>
-      <c r="C23" t="n">
-        <v>4</v>
+        <v>34</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>34</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>68</v>
-      </c>
-      <c r="C25" t="n">
-        <v>4</v>
+        <v>63</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>32</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>31</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="D26" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brian Plaatjies</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>33</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>36</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>36</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kirsten Jacobs</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>36</v>
+      </c>
+      <c r="D28" t="n">
+        <v>32</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -830,10 +1222,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>-100</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="3">
@@ -843,10 +1235,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>-96</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -856,101 +1248,101 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>-72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>-60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>-52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>-60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>-52</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>-78</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>-66</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>-66</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="12">
@@ -960,36 +1352,36 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>-62</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>-62</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>-62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -999,10 +1391,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>-28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -1012,36 +1404,36 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>128</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -1051,10 +1443,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>166</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20">
@@ -1064,10 +1456,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>-110</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="21">
@@ -1077,10 +1469,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="22">
@@ -1090,10 +1482,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>-82</v>
+        <v>-41</v>
       </c>
     </row>
     <row r="23">
@@ -1103,10 +1495,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>-18</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="24">
@@ -1116,10 +1508,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>-112</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="25">
@@ -1129,10 +1521,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1142,10 +1534,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>148</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -1155,10 +1547,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28">
@@ -1168,10 +1560,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1609,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3">
@@ -1232,13 +1624,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Home Boys</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1247,13 +1639,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Home Boys</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1262,7 +1654,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6">
@@ -1277,7 +1669,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1292,7 +1684,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8">
@@ -1307,7 +1699,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -1322,13 +1714,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Fairway Fighters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1337,13 +1729,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fairway Fighters</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1352,7 +1744,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -1367,13 +1759,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tee Stingers</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1382,13 +1774,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Tee Stingers</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1397,7 +1789,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -1412,7 +1804,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1819,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -1442,7 +1834,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18">
@@ -1457,7 +1849,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -1472,7 +1864,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -1487,7 +1879,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21">
@@ -1502,7 +1894,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -1592,13 +1984,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tee Stingers</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1607,13 +1999,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Tee Stingers</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1622,7 +2014,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
@@ -1637,7 +2029,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>82</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -1652,7 +2044,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1666,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2092,408 +2484,6 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>90</v>
-      </c>
-      <c r="C25" t="n">
-        <v>40</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>88</v>
-      </c>
-      <c r="C26" t="n">
-        <v>36</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>91</v>
-      </c>
-      <c r="C27" t="n">
-        <v>36</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>John Barker</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>86</v>
-      </c>
-      <c r="C28" t="n">
-        <v>36</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>93</v>
-      </c>
-      <c r="C29" t="n">
-        <v>35</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>96</v>
-      </c>
-      <c r="C30" t="n">
-        <v>35</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>89</v>
-      </c>
-      <c r="C31" t="n">
-        <v>35</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Fuad Adams</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>93</v>
-      </c>
-      <c r="C32" t="n">
-        <v>34</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>97</v>
-      </c>
-      <c r="C33" t="n">
-        <v>33</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>87</v>
-      </c>
-      <c r="C34" t="n">
-        <v>33</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>92</v>
-      </c>
-      <c r="C35" t="n">
-        <v>32</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Godfrey Daniels</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>99</v>
-      </c>
-      <c r="C36" t="n">
-        <v>31</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>102</v>
-      </c>
-      <c r="C37" t="n">
-        <v>30</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>92</v>
-      </c>
-      <c r="C38" t="n">
-        <v>29</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>96</v>
-      </c>
-      <c r="C39" t="n">
-        <v>28</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>103</v>
-      </c>
-      <c r="C40" t="n">
-        <v>28</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>98</v>
-      </c>
-      <c r="C41" t="n">
-        <v>25</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Brian Plaatjies</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>105</v>
-      </c>
-      <c r="C42" t="n">
-        <v>24</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>98</v>
-      </c>
-      <c r="C43" t="n">
-        <v>24</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>99</v>
-      </c>
-      <c r="C44" t="n">
-        <v>19</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Lenny Booysen</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>112</v>
-      </c>
-      <c r="C45" t="n">
-        <v>15</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>112</v>
-      </c>
-      <c r="C46" t="n">
-        <v>14</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2506,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2796,276 +2786,6 @@
         <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>John Barker</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>80</v>
-      </c>
-      <c r="C17" t="n">
-        <v>38</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>85</v>
-      </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ronny Kaptein</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>88</v>
-      </c>
-      <c r="C19" t="n">
-        <v>34</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Shawn Davies</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>79</v>
-      </c>
-      <c r="C20" t="n">
-        <v>32</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>94</v>
-      </c>
-      <c r="C21" t="n">
-        <v>32</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>99</v>
-      </c>
-      <c r="C22" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>112</v>
-      </c>
-      <c r="C23" t="n">
-        <v>30</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>87</v>
-      </c>
-      <c r="C24" t="n">
-        <v>28</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>93</v>
-      </c>
-      <c r="C25" t="n">
-        <v>26</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>90</v>
-      </c>
-      <c r="C26" t="n">
-        <v>25</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>96</v>
-      </c>
-      <c r="C27" t="n">
-        <v>24</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>104</v>
-      </c>
-      <c r="C28" t="n">
-        <v>24</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>100</v>
-      </c>
-      <c r="C29" t="n">
-        <v>24</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>110</v>
-      </c>
-      <c r="C30" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>102</v>
-      </c>
-      <c r="C31" t="n">
-        <v>16</v>
-      </c>
-      <c r="D31" t="inlineStr">
         <is>
           <t>Tee Tigers</t>
         </is>
@@ -3082,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3318,222 +3038,6 @@
         <v>24</v>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>90</v>
-      </c>
-      <c r="C14" t="n">
-        <v>37</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>83</v>
-      </c>
-      <c r="C15" t="n">
-        <v>37</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>36</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>93</v>
-      </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>94</v>
-      </c>
-      <c r="C19" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>90</v>
-      </c>
-      <c r="C20" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>93</v>
-      </c>
-      <c r="C21" t="n">
-        <v>29</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>28</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>99</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>94</v>
-      </c>
-      <c r="C24" t="n">
-        <v>25</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>104</v>
-      </c>
-      <c r="C25" t="n">
-        <v>24</v>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t>Tee Tigers</t>
         </is>
@@ -3550,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3968,404 +3472,6 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>87</v>
-      </c>
-      <c r="C25" t="n">
-        <v>35</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>90</v>
-      </c>
-      <c r="C26" t="n">
-        <v>35</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>81</v>
-      </c>
-      <c r="C27" t="n">
-        <v>35</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>87</v>
-      </c>
-      <c r="C28" t="n">
-        <v>32</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>96</v>
-      </c>
-      <c r="C29" t="n">
-        <v>32</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>91</v>
-      </c>
-      <c r="C30" t="n">
-        <v>31</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Shawn Davies</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>82</v>
-      </c>
-      <c r="C31" t="n">
-        <v>31</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Lenny Booysen</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>106</v>
-      </c>
-      <c r="C32" t="n">
-        <v>30</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>95</v>
-      </c>
-      <c r="C33" t="n">
-        <v>30</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>93</v>
-      </c>
-      <c r="C34" t="n">
-        <v>29</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>94</v>
-      </c>
-      <c r="C35" t="n">
-        <v>28</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>95</v>
-      </c>
-      <c r="C36" t="n">
-        <v>27</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>100</v>
-      </c>
-      <c r="C37" t="n">
-        <v>27</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>101</v>
-      </c>
-      <c r="C38" t="n">
-        <v>26</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>102</v>
-      </c>
-      <c r="C39" t="n">
-        <v>23</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>100</v>
-      </c>
-      <c r="C40" t="n">
-        <v>22</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>115</v>
-      </c>
-      <c r="C41" t="n">
-        <v>22</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Godfrey Daniels</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>108</v>
-      </c>
-      <c r="C42" t="n">
-        <v>20</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Kirsten Jacobs</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>103</v>
-      </c>
-      <c r="C43" t="n">
-        <v>23</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Fuad Adams</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
         <is>
           <t>Fairway Fighters</t>
         </is>
@@ -4382,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4762,366 +3868,6 @@
         <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>John Barker</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Ronny Kaptein</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Shawn Davies</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Godfrey Daniels</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr">
         <is>
           <t>Tee Stingers</t>
         </is>
@@ -5138,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5379,222 +4125,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>90</v>
-      </c>
-      <c r="C14" t="n">
-        <v>37</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>83</v>
-      </c>
-      <c r="C15" t="n">
-        <v>37</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>36</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>95</v>
-      </c>
-      <c r="C17" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>93</v>
-      </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>94</v>
-      </c>
-      <c r="C19" t="n">
-        <v>31</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>90</v>
-      </c>
-      <c r="C20" t="n">
-        <v>29</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>93</v>
-      </c>
-      <c r="C21" t="n">
-        <v>29</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>28</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>99</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>94</v>
-      </c>
-      <c r="C24" t="n">
-        <v>25</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>104</v>
-      </c>
-      <c r="C25" t="n">
-        <v>24</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -14,8 +14,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +455,6 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>Rounds_Played</t>
         </is>
       </c>
@@ -487,11 +475,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +485,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
         <v>36</v>
@@ -516,13 +500,7 @@
         <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>37</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -532,7 +510,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C4" t="n">
         <v>35</v>
@@ -544,12 +522,8 @@
       <c r="F4" t="n">
         <v>23</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>24</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4</v>
+      <c r="G4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +533,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -570,13 +544,7 @@
         <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>34</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -594,9 +562,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -607,7 +573,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
         <v>29</v>
@@ -619,12 +585,8 @@
       <c r="F7" t="n">
         <v>28</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
+      <c r="G7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -634,7 +596,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -645,13 +607,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>37</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -674,11 +630,7 @@
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -688,7 +640,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -698,12 +650,8 @@
         <v>31</v>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>31</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
+      <c r="G10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -726,11 +674,7 @@
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -748,9 +692,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
+      <c r="G12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -772,11 +714,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -786,7 +724,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="C14" t="n">
         <v>35</v>
@@ -801,13 +739,7 @@
         <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>27</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -828,11 +760,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -850,9 +778,7 @@
       <c r="F16" t="n">
         <v>23</v>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
+      <c r="G16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -876,11 +802,7 @@
         <v>29</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -900,9 +822,7 @@
       <c r="F18" t="n">
         <v>30</v>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
+      <c r="G18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -913,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="C19" t="n">
         <v>35</v>
@@ -928,13 +848,7 @@
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>35</v>
-      </c>
-      <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -944,7 +858,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C20" t="n">
         <v>33</v>
@@ -959,13 +873,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>29</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -988,11 +896,7 @@
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1002,7 +906,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="C22" t="n">
         <v>25</v>
@@ -1017,13 +921,7 @@
         <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>29</v>
-      </c>
-      <c r="I22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1042,11 +940,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1056,7 +950,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="C24" t="n">
         <v>28</v>
@@ -1069,13 +963,7 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>28</v>
-      </c>
-      <c r="I24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1096,11 +984,7 @@
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1123,11 +1007,7 @@
         <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1137,7 +1017,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="C27" t="n">
         <v>33</v>
@@ -1150,13 +1030,7 @@
         <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>36</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1177,11 +1051,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1222,10 +1092,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>-6</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -1235,10 +1105,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -1248,10 +1118,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
@@ -1261,10 +1131,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -1274,101 +1144,101 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>54</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>-31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>-21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>-12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>-8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>-6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -1378,166 +1248,166 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>-55</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>-50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>-41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>-9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>-56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>74</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -1577,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1895,156 +1765,6 @@
       </c>
       <c r="C21" t="n">
         <v>76</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Sheet2</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3480,652 +3200,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Strokes</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>John Barker</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ronny Kaptein</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Shawn Davies</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Godfrey Daniels</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Strokes</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>90</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>83</v>
-      </c>
-      <c r="C3" t="n">
-        <v>37</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>93</v>
-      </c>
-      <c r="C4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>95</v>
-      </c>
-      <c r="C5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>94</v>
-      </c>
-      <c r="C7" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>90</v>
-      </c>
-      <c r="C8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>93</v>
-      </c>
-      <c r="C9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>95</v>
-      </c>
-      <c r="C10" t="n">
-        <v>28</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>99</v>
-      </c>
-      <c r="C11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>94</v>
-      </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>104</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -1065,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1076,364 +1076,628 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Best6_Strokes_Over_Par</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PGC</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Games_Played</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Best6_Strokes_Over_Par</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arno Adonis</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>31</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mika Moerat</t>
+          <t>Arno Adonis</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G3" t="n">
         <v>4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>21</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F4" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>98</v>
+        <v>39</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Brian Plaatjies</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>33</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>22</v>
+      </c>
+      <c r="F7" t="n">
+        <v>22</v>
+      </c>
+      <c r="G7" t="n">
         <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>64</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G9" t="n">
         <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>48</v>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
         <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>90</v>
+      </c>
+      <c r="C11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>28</v>
+      </c>
+      <c r="G11" t="n">
         <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>21</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>27</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>17</v>
+      </c>
+      <c r="D14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>14</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Kirsten Jacobs</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>90</v>
+        <v>31</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>31</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>66</v>
+      </c>
+      <c r="C17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G17" t="n">
         <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>74</v>
+      </c>
+      <c r="C18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>34</v>
+      </c>
+      <c r="G18" t="n">
         <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27</v>
+      </c>
+      <c r="E19" t="n">
+        <v>23</v>
+      </c>
+      <c r="F19" t="n">
+        <v>24</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>15</v>
+      </c>
+      <c r="D20" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>123</v>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>40</v>
+      </c>
+      <c r="D21" t="n">
+        <v>40</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>43</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="D22" t="n">
+        <v>30</v>
+      </c>
+      <c r="E22" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" t="n">
+        <v>28</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" t="n">
-        <v>39</v>
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
+        <v>24</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>7</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" t="n">
         <v>2</v>
-      </c>
-      <c r="C25" t="n">
-        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="D26" t="n">
+        <v>38</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kirsten Jacobs</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" t="n">
+        <v>29</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brian Plaatjies</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C28" t="n">
-        <v>33</v>
+        <v>19</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -2043,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2054,12 +2054,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Course</t>
+          <t>LIV Total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LIV_Points</t>
+          <t>Strength Index</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Akasia</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Kyalami</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PGC</t>
         </is>
       </c>
     </row>
@@ -2069,13 +2094,28 @@
           <t>Fairway Fighters</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Akasia</t>
-        </is>
+      <c r="B2" t="n">
+        <v>389</v>
       </c>
       <c r="C2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>108</v>
+      </c>
+      <c r="F2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G2" t="n">
+        <v>103</v>
+      </c>
+      <c r="H2" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="3">
@@ -2084,43 +2124,88 @@
           <t>Tee Stingers</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Akasia</t>
-        </is>
+      <c r="B3" t="n">
+        <v>334</v>
       </c>
       <c r="C3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>104</v>
+      </c>
+      <c r="F3" t="n">
+        <v>81</v>
+      </c>
+      <c r="G3" t="n">
+        <v>63</v>
+      </c>
+      <c r="H3" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Akasia</t>
-        </is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>333</v>
       </c>
       <c r="C4" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>102</v>
+      </c>
+      <c r="F4" t="n">
+        <v>102</v>
+      </c>
+      <c r="G4" t="n">
+        <v>53</v>
+      </c>
+      <c r="H4" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Akasia</t>
-        </is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>309</v>
       </c>
       <c r="C5" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H5" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -2129,238 +2214,28 @@
           <t>Birdie Buddies</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Akasia</t>
-        </is>
+      <c r="B6" t="n">
+        <v>294</v>
       </c>
       <c r="C6" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>57</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="F6" t="n">
         <v>56</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="G6" t="n">
         <v>87</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+      <c r="H6" t="n">
         <v>94</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CopperLeaf</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -454,11 +454,6 @@
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Rounds_Played</t>
         </is>
@@ -480,15 +475,12 @@
         <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -508,15 +500,12 @@
         <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
-      </c>
-      <c r="H3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -536,15 +525,12 @@
         <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
-      </c>
-      <c r="H4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -564,15 +550,12 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
-      </c>
-      <c r="H5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -592,15 +575,12 @@
         <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
-      </c>
-      <c r="H6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -620,15 +600,12 @@
         <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -648,15 +625,12 @@
         <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -676,15 +650,12 @@
         <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
-      </c>
-      <c r="H9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -704,15 +675,12 @@
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -732,15 +700,12 @@
         <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
-      </c>
-      <c r="H11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -760,15 +725,12 @@
         <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
-      </c>
-      <c r="H12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -788,15 +750,12 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -816,15 +775,12 @@
         <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -844,15 +800,12 @@
         <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
-      </c>
-      <c r="H15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -872,15 +825,12 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
-      </c>
-      <c r="H16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -900,15 +850,12 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
         <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
-      </c>
-      <c r="H17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -928,15 +875,12 @@
         <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -956,15 +900,12 @@
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
-      </c>
-      <c r="H19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -984,15 +925,12 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
-      </c>
-      <c r="H20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1018,9 +956,6 @@
         <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1040,15 +975,12 @@
         <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1068,15 +1000,12 @@
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1102,9 +1031,6 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1124,15 +1050,12 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1158,9 +1081,6 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1186,9 +1106,6 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1208,15 +1125,12 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>23</v>
-      </c>
-      <c r="H28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1231,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1257,7 +1171,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CopperLeaf</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1266,11 +1180,6 @@
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>PGC</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Games_Played</t>
         </is>
@@ -1292,15 +1201,12 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1320,15 +1226,12 @@
         <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1348,15 +1251,12 @@
         <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
-      </c>
-      <c r="H4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1376,15 +1276,12 @@
         <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
-      </c>
-      <c r="H5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1404,15 +1301,12 @@
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
         <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>28</v>
-      </c>
-      <c r="H6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1432,15 +1326,12 @@
         <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1466,9 +1357,6 @@
         <v>22</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1488,15 +1376,12 @@
         <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>22</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
-      </c>
-      <c r="H9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1516,15 +1401,12 @@
         <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1544,15 +1426,12 @@
         <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
-      </c>
-      <c r="H11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1572,15 +1451,12 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1600,15 +1476,12 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>29</v>
-      </c>
-      <c r="H13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1628,15 +1501,12 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>23</v>
-      </c>
-      <c r="H14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1656,15 +1526,12 @@
         <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
         <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1684,15 +1551,12 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>28</v>
-      </c>
-      <c r="H16" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1712,15 +1576,12 @@
         <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>43</v>
-      </c>
-      <c r="H17" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1740,15 +1601,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
-      </c>
-      <c r="H18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1774,9 +1632,6 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1796,15 +1651,12 @@
         <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1830,9 +1682,6 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1852,15 +1701,12 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
-      </c>
-      <c r="H22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1880,15 +1726,12 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
         <v>21</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
-      </c>
-      <c r="H23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1908,15 +1751,12 @@
         <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>36</v>
-      </c>
-      <c r="H24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1936,15 +1776,12 @@
         <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>34</v>
-      </c>
-      <c r="H25" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1964,15 +1801,12 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1992,15 +1826,12 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>31</v>
-      </c>
-      <c r="H27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2026,9 +1857,6 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2043,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2074,17 +1902,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>CopperLeaf</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>Kyalami</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>PGC</t>
         </is>
       </c>
     </row>
@@ -2109,14 +1932,11 @@
         <v>108</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
         <v>103</v>
       </c>
-      <c r="H2" t="n">
-        <v>102</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2139,14 +1959,11 @@
         <v>104</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
         <v>63</v>
       </c>
-      <c r="H3" t="n">
-        <v>86</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2169,14 +1986,11 @@
         <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>53</v>
       </c>
-      <c r="H4" t="n">
-        <v>76</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2199,14 +2013,11 @@
         <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
         <v>37</v>
       </c>
-      <c r="H5" t="n">
-        <v>86</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2229,13 +2040,10 @@
         <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="G6" t="n">
         <v>87</v>
-      </c>
-      <c r="H6" t="n">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Trend Index</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -1918,14 +1918,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>389</v>
+        <v>313</v>
       </c>
       <c r="C2" t="n">
-        <v>97.2</v>
+        <v>104.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>334</v>
+        <v>253</v>
       </c>
       <c r="C3" t="n">
-        <v>83.5</v>
+        <v>84.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1968,41 +1968,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="C4" t="n">
-        <v>83.2</v>
+        <v>79.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Home Boys</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>309</v>
+        <v>231</v>
       </c>
       <c r="C5" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2013,23 +2013,23 @@
         <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Home Boys</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>73.5</v>
+        <v>75</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="F6" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -11,9 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strokes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIV" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akasia" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +468,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="D2" t="n">
         <v>36</v>
@@ -481,7 +480,7 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -494,7 +493,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
         <v>35</v>
@@ -506,7 +505,7 @@
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -519,7 +518,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="D4" t="n">
         <v>33</v>
@@ -531,7 +530,7 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -540,23 +539,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -565,20 +564,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
         <v>3</v>
@@ -590,23 +589,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -615,20 +614,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -640,20 +639,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -665,23 +664,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>35</v>
       </c>
-      <c r="E10" t="n">
-        <v>23</v>
-      </c>
       <c r="F10" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -690,23 +689,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -715,23 +714,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -740,23 +739,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -765,17 +764,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -790,23 +789,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -815,23 +814,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -840,20 +839,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -865,23 +864,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -890,23 +889,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -915,17 +914,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -940,23 +939,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -965,23 +964,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -990,17 +989,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1015,23 +1014,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1040,14 +1039,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1056,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1065,14 +1064,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Brian Plaatjies</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1081,7 +1080,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1090,47 +1089,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brian Plaatjies</t>
+          <t>Kirsten Jacobs</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Kirsten Jacobs</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>23</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>23</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1145,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,7 +1169,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -1207,7 +1181,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1220,7 +1194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -1232,7 +1206,7 @@
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1241,23 +1215,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1266,23 +1240,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1291,23 +1265,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1316,20 +1290,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -1341,20 +1315,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -1366,20 +1340,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>
@@ -1391,20 +1365,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
@@ -1416,23 +1390,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1441,23 +1415,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1466,23 +1440,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1491,23 +1465,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
         <v>18</v>
       </c>
-      <c r="E14" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1516,23 +1490,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F15" t="n">
         <v>21</v>
       </c>
-      <c r="E15" t="n">
-        <v>30</v>
-      </c>
-      <c r="F15" t="n">
-        <v>32</v>
-      </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1541,23 +1515,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1566,23 +1540,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1591,20 +1565,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
@@ -1616,17 +1590,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>48</v>
+      </c>
+      <c r="D19" t="n">
+        <v>27</v>
+      </c>
+      <c r="E19" t="n">
         <v>21</v>
-      </c>
-      <c r="D19" t="n">
-        <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1641,17 +1615,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1666,17 +1640,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1691,20 +1665,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
@@ -1716,20 +1690,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1741,23 +1715,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1766,23 +1740,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1791,17 +1765,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Kirsten Jacobs</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1816,47 +1790,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kirsten Jacobs</t>
+          <t>Brian Plaatjies</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E27" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Brian Plaatjies</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>33</v>
-      </c>
-      <c r="D28" t="n">
-        <v>33</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2495,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2523,18 +2472,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Fairway Fighters</t>
         </is>
       </c>
     </row>
@@ -2545,10 +2494,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2559,68 +2508,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Tee Stingers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Fairway Fighters</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tee Stingers</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2631,68 +2580,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Fairway Fighters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mika Moerat</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fairway Fighters</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Home Boys</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2703,14 +2652,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2721,7 +2670,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2731,60 +2680,6 @@
         <v>24</v>
       </c>
       <c r="D13" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>100</v>
-      </c>
-      <c r="C14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>110</v>
-      </c>
-      <c r="C15" t="n">
-        <v>18</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>102</v>
-      </c>
-      <c r="C16" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" t="inlineStr">
         <is>
           <t>Tee Tigers</t>
         </is>
@@ -2801,258 +2696,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Strokes</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>IPS</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>90</v>
-      </c>
-      <c r="C2" t="n">
-        <v>37</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>83</v>
-      </c>
-      <c r="C3" t="n">
-        <v>37</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>93</v>
-      </c>
-      <c r="C4" t="n">
-        <v>36</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>95</v>
-      </c>
-      <c r="C5" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>93</v>
-      </c>
-      <c r="C6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>94</v>
-      </c>
-      <c r="C7" t="n">
-        <v>31</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>90</v>
-      </c>
-      <c r="C8" t="n">
-        <v>29</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>93</v>
-      </c>
-      <c r="C9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>95</v>
-      </c>
-      <c r="C10" t="n">
-        <v>28</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>99</v>
-      </c>
-      <c r="C11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>94</v>
-      </c>
-      <c r="C12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Birdie Buddies</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>104</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Tee Tigers</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strokes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIV" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akasia" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +455,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Rounds_Played</t>
         </is>
       </c>
@@ -468,7 +474,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="D2" t="n">
         <v>36</v>
@@ -480,7 +486,10 @@
         <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -493,7 +502,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="D3" t="n">
         <v>35</v>
@@ -505,7 +514,10 @@
         <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +530,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="D4" t="n">
         <v>33</v>
@@ -530,7 +542,10 @@
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -539,23 +554,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -564,22 +582,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -589,23 +610,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -614,22 +638,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -639,22 +666,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -664,23 +694,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -689,23 +722,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -714,23 +750,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -739,23 +778,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -764,22 +806,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -789,23 +834,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -814,23 +862,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -839,22 +890,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -864,23 +918,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -889,23 +946,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
         <v>30</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
+      <c r="H19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -914,22 +974,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -939,23 +1002,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -964,23 +1030,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D22" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -989,22 +1058,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1014,23 +1086,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1039,14 +1114,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1055,7 +1130,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1064,14 +1142,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Brian Plaatjies</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1080,7 +1158,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1089,22 +1170,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Brian Plaatjies</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Kirsten Jacobs</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>23</v>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>23</v>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1119,7 +1231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1267,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Games_Played</t>
         </is>
       </c>
@@ -1169,7 +1286,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -1181,7 +1298,10 @@
         <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1194,7 +1314,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -1206,7 +1326,10 @@
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>15</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1215,23 +1338,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1240,23 +1366,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" t="n">
         <v>27</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
+      <c r="H5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1265,23 +1394,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1290,22 +1422,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1315,22 +1450,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1340,22 +1478,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1365,22 +1506,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>21</v>
       </c>
-      <c r="E10" t="n">
-        <v>30</v>
-      </c>
-      <c r="F10" t="n">
-        <v>32</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1390,23 +1534,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1415,23 +1562,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1440,23 +1590,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1465,23 +1618,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1490,23 +1646,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1515,23 +1674,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1540,23 +1702,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>123</v>
+      </c>
+      <c r="D17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" t="n">
         <v>43</v>
       </c>
-      <c r="D17" t="n">
-        <v>20</v>
-      </c>
-      <c r="E17" t="n">
-        <v>23</v>
-      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1565,22 +1730,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1590,22 +1758,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1615,22 +1786,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1640,22 +1814,25 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1665,22 +1842,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1690,22 +1870,25 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1715,23 +1898,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1740,23 +1926,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1765,22 +1954,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kirsten Jacobs</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1790,22 +1982,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Kirsten Jacobs</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>31</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>31</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Brian Plaatjies</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C28" t="n">
         <v>33</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>33</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1820,7 +2043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,6 +2082,11 @@
           <t>Kyalami</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CopperLeaf</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1867,10 +2095,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>313</v>
+        <v>389</v>
       </c>
       <c r="C2" t="n">
-        <v>104.3</v>
+        <v>97.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1886,6 +2114,9 @@
       <c r="G2" t="n">
         <v>103</v>
       </c>
+      <c r="H2" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1894,10 +2125,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>253</v>
+        <v>334</v>
       </c>
       <c r="C3" t="n">
-        <v>84.3</v>
+        <v>83.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1913,18 +2144,21 @@
       <c r="G3" t="n">
         <v>63</v>
       </c>
+      <c r="H3" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>238</v>
+        <v>333</v>
       </c>
       <c r="C4" t="n">
-        <v>79.3</v>
+        <v>83.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1932,53 +2166,59 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>53</v>
+      </c>
+      <c r="H4" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Home Boys</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>309</v>
       </c>
       <c r="C5" t="n">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>102</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>53</v>
+        <v>37</v>
+      </c>
+      <c r="H5" t="n">
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Home Boys</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>75</v>
+        <v>73.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1986,13 +2226,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G6" t="n">
-        <v>37</v>
+        <v>87</v>
+      </c>
+      <c r="H6" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2472,18 +2715,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fairway Fighters</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
     </row>
@@ -2494,10 +2737,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2508,68 +2751,68 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tee Stingers</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lucien Barnes</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fairway Fighters</t>
+          <t>Birdie Buddies</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Tee Stingers</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2580,68 +2823,68 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mika Moerat</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Fairway Fighters</t>
+          <t>Tee Tigers</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ranzel Louw</t>
+          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tee Tigers</t>
+          <t>Fairway Fighters</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Birdie Buddies</t>
+          <t>Home Boys</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jodi Van Niekerk</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2652,14 +2895,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2670,7 +2913,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2680,6 +2923,60 @@
         <v>24</v>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>110</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>102</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Tee Tigers</t>
         </is>
@@ -2696,6 +2993,258 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>90</v>
+      </c>
+      <c r="C2" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>36</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C5" t="n">
+        <v>35</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>94</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" t="n">
+        <v>29</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>99</v>
+      </c>
+      <c r="C11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,35 +430,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Pos Change</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Best6_IPS</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Akasia</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PGC</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Kyalami</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CopperLeaf</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Rounds_Played</t>
         </is>
@@ -470,25 +475,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Arno Adonis</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>139</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>36</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>37</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>34</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -498,25 +508,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>Lucien Barnes</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>132</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>35</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>32</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>35</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>30</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -526,25 +541,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Mika Moerat</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>125</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>33</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>35</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>29</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>28</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -554,25 +574,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Jodi Van Niekerk</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>117</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>35</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>31</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>27</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>24</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -582,25 +607,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Warren Lottering</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>95</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>33</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>26</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>36</v>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -610,25 +640,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Ranzel Louw</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>92</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>25</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>22</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>16</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -638,25 +673,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Trevor Meyer</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>88</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>40</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>30</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>18</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -666,25 +706,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>Dale Adonis</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>85</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>32</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>27</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>26</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -694,25 +739,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>Ashley Spocter</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>82</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>35</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>23</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>24</v>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -722,25 +772,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Byron Labuschagne</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>82</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>29</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>28</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>25</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -750,25 +805,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Eugene Dudley</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>81</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>30</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>27</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>24</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -778,25 +838,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>Shaheen Boughan</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>80</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>28</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>24</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -806,25 +871,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>John Barker</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>74</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>36</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>38</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -834,25 +904,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Laurent Changuion</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>73</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>19</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>29</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>25</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -862,25 +937,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>Chad Naude</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>72</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>35</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>37</v>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -890,25 +970,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>Bjorn Singh</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>69</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>35</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>34</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -918,25 +1003,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>Winston Willemse</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>68</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>36</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>32</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>3</v>
       </c>
     </row>
@@ -946,25 +1036,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>Pieter Gagiano</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>66</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>14</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>22</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>30</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -974,25 +1069,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Shawn Davies</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>63</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>31</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>32</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1002,25 +1102,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>Dewald Van Rooyen</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>55</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>24</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
         <v>31</v>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1030,25 +1135,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Godfrey Daniels</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>51</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>31</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>20</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1058,25 +1168,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Lenny Booysen</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>45</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>15</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>30</v>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1086,17 +1201,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Fuad Adams</t>
         </is>
-      </c>
-      <c r="C24" t="n">
-        <v>34</v>
       </c>
       <c r="D24" t="n">
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1105,6 +1222,9 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1114,15 +1234,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Ronny Kaptein</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>34</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
@@ -1130,9 +1252,12 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>34</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1142,17 +1267,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>Arn Smith</t>
         </is>
-      </c>
-      <c r="C26" t="n">
-        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>28</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1161,6 +1288,9 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1170,17 +1300,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>Brian Plaatjies</t>
         </is>
-      </c>
-      <c r="C27" t="n">
-        <v>24</v>
       </c>
       <c r="D27" t="n">
         <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1189,6 +1321,9 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1198,25 +1333,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>Kirsten Jacobs</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>23</v>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>23</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -419,51 +419,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Pos Change</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Best6_IPS</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Akasia</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PGC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Kyalami</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CopperLeaf</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Rounds_Played</t>
         </is>
@@ -475,30 +480,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Arno Adonis</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>139</v>
       </c>
       <c r="E2" t="n">
+        <v>139</v>
+      </c>
+      <c r="F2" t="n">
         <v>36</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>32</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>37</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>34</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -508,30 +516,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lucien Barnes</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>132</v>
       </c>
       <c r="E3" t="n">
+        <v>132</v>
+      </c>
+      <c r="F3" t="n">
         <v>35</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>32</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>35</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>30</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -541,30 +552,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Mika Moerat</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>125</v>
       </c>
       <c r="E4" t="n">
+        <v>125</v>
+      </c>
+      <c r="F4" t="n">
         <v>33</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>35</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>29</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>28</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -574,30 +588,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Jodi Van Niekerk</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>117</v>
       </c>
       <c r="E5" t="n">
+        <v>117</v>
+      </c>
+      <c r="F5" t="n">
         <v>35</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>31</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>27</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>24</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>4</v>
       </c>
     </row>
@@ -607,30 +624,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
+        <v>95</v>
+      </c>
+      <c r="F6" t="n">
         <v>33</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>26</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>36</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -640,30 +660,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ranzel Louw</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>92</v>
       </c>
       <c r="E7" t="n">
+        <v>92</v>
+      </c>
+      <c r="F7" t="n">
         <v>25</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>22</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>29</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -673,30 +696,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>88</v>
       </c>
       <c r="E8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F8" t="n">
         <v>40</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>30</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>18</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -706,30 +732,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>85</v>
       </c>
       <c r="E9" t="n">
+        <v>85</v>
+      </c>
+      <c r="F9" t="n">
         <v>32</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>27</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>26</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>3</v>
       </c>
     </row>
@@ -739,30 +768,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Ashley Spocter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>82</v>
       </c>
       <c r="E10" t="n">
+        <v>82</v>
+      </c>
+      <c r="F10" t="n">
         <v>35</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>23</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>24</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -772,30 +804,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>Byron Labuschagne</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>82</v>
       </c>
       <c r="E11" t="n">
+        <v>82</v>
+      </c>
+      <c r="F11" t="n">
         <v>29</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>28</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>25</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -805,30 +840,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>81</v>
       </c>
       <c r="E12" t="n">
+        <v>81</v>
+      </c>
+      <c r="F12" t="n">
         <v>30</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>27</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>24</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
     </row>
@@ -838,30 +876,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>80</v>
       </c>
       <c r="E13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" t="n">
         <v>28</v>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>28</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>24</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>3</v>
       </c>
     </row>
@@ -871,30 +912,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>John Barker</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>74</v>
       </c>
       <c r="E14" t="n">
+        <v>74</v>
+      </c>
+      <c r="F14" t="n">
         <v>36</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>38</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -904,30 +948,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>73</v>
       </c>
       <c r="E15" t="n">
+        <v>73</v>
+      </c>
+      <c r="F15" t="n">
         <v>19</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>29</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>25</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -937,30 +984,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Chad Naude</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>35</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>37</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -970,30 +1020,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>35</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>34</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1003,31 +1056,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>68</v>
       </c>
       <c r="E18" t="n">
+        <v>68</v>
+      </c>
+      <c r="F18" t="n">
         <v>36</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>32</v>
       </c>
-      <c r="I18" t="n">
-        <v>3</v>
+      <c r="J18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1036,30 +1092,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>66</v>
       </c>
       <c r="E19" t="n">
+        <v>66</v>
+      </c>
+      <c r="F19" t="n">
         <v>14</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>22</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>30</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1069,30 +1128,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>31</v>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>32</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1102,31 +1164,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>Dewald Van Rooyen</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>55</v>
       </c>
       <c r="E21" t="n">
+        <v>55</v>
+      </c>
+      <c r="F21" t="n">
         <v>24</v>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>31</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1135,30 +1200,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>51</v>
       </c>
       <c r="E22" t="n">
+        <v>51</v>
+      </c>
+      <c r="F22" t="n">
         <v>31</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1168,30 +1236,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Lenny Booysen</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>45</v>
       </c>
       <c r="E23" t="n">
+        <v>45</v>
+      </c>
+      <c r="F23" t="n">
         <v>15</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>30</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1201,12 +1272,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1216,7 +1287,7 @@
         <v>34</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1225,7 +1296,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1234,19 +1308,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1255,9 +1329,12 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>34</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1267,12 +1344,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1282,7 +1359,7 @@
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1291,7 +1368,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1300,12 +1380,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Brian Plaatjies</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brian Plaatjies</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1315,7 +1395,7 @@
         <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1324,6 +1404,9 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1333,30 +1416,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>Kirsten Jacobs</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Kirsten Jacobs</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>23</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
         <v>23</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1562,23 +1648,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -1590,23 +1676,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -1618,23 +1704,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -1646,23 +1732,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>23</v>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -1674,23 +1760,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
+        <v>29</v>
+      </c>
+      <c r="F11" t="n">
         <v>21</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -1702,23 +1788,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -1730,20 +1816,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1758,23 +1844,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
@@ -1786,23 +1872,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -1814,26 +1900,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1842,26 +1928,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1870,23 +1956,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>2</v>
@@ -1898,20 +1984,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>39</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
         <v>21</v>
-      </c>
-      <c r="D19" t="n">
-        <v>21</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1926,23 +2012,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>41</v>
+      </c>
+      <c r="D20" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>22</v>
-      </c>
-      <c r="D20" t="n">
-        <v>14</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
@@ -1954,20 +2040,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1982,20 +2068,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -2010,20 +2096,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2038,26 +2124,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2066,17 +2152,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2085,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2094,14 +2180,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2110,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>1</v>
@@ -2389,7 +2475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2809,12 +2895,6 @@
           <t>Tee Tigers</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3385,7 +3465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3752,62 +3832,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Winston Willemse</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Tee Stingers</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fuad Adams</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Arn Smith</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Home Boys</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dewald Van Rooyen</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fairway Fighters</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/GOAM_Scores_2026_May_updated.xlsx
+++ b/data/GOAM_Scores_2026_May_updated.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IPS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strokes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LIV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Akasia" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PGC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IPS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Strokes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LIV" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Akasia" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CopperLeaf" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Kyalami" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PGC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Services" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,40 +436,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Pos Change</t>
+          <t>IPS</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>IPS</t>
+          <t>Best6_IPS</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Best6_IPS</t>
+          <t>Akasia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Akasia</t>
+          <t>PGC</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>PGC</t>
+          <t>Kyalami</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Kyalami</t>
+          <t>CopperLeaf</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>CopperLeaf</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Rounds_Played</t>
         </is>
@@ -483,31 +479,26 @@
           <t>Arno Adonis</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C2" t="n">
+        <v>139</v>
       </c>
       <c r="D2" t="n">
         <v>139</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -519,31 +510,26 @@
           <t>Lucien Barnes</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C3" t="n">
+        <v>132</v>
       </c>
       <c r="D3" t="n">
         <v>132</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" t="n">
         <v>35</v>
       </c>
-      <c r="G3" t="n">
-        <v>32</v>
-      </c>
       <c r="H3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -555,31 +541,26 @@
           <t>Mika Moerat</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C4" t="n">
+        <v>125</v>
       </c>
       <c r="D4" t="n">
         <v>125</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
-        <v>28</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -591,31 +572,26 @@
           <t>Jodi Van Niekerk</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C5" t="n">
+        <v>117</v>
       </c>
       <c r="D5" t="n">
         <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -627,31 +603,26 @@
           <t>Warren Lottering</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C6" t="n">
+        <v>95</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +634,26 @@
           <t>Ranzel Louw</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C7" t="n">
+        <v>92</v>
       </c>
       <c r="D7" t="n">
         <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -699,31 +665,26 @@
           <t>Trevor Meyer</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C8" t="n">
+        <v>88</v>
       </c>
       <c r="D8" t="n">
         <v>88</v>
       </c>
       <c r="E8" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -735,31 +696,26 @@
           <t>Dale Adonis</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C9" t="n">
+        <v>85</v>
       </c>
       <c r="D9" t="n">
         <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -771,30 +727,25 @@
           <t>Ashley Spocter</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C10" t="n">
+        <v>82</v>
       </c>
       <c r="D10" t="n">
         <v>82</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -807,30 +758,25 @@
           <t>Byron Labuschagne</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C11" t="n">
+        <v>82</v>
       </c>
       <c r="D11" t="n">
         <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -843,31 +789,26 @@
           <t>Eugene Dudley</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C12" t="n">
+        <v>81</v>
       </c>
       <c r="D12" t="n">
         <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -879,31 +820,26 @@
           <t>Shaheen Boughan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C13" t="n">
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>80</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>28</v>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
       <c r="H13" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -915,31 +851,26 @@
           <t>John Barker</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C14" t="n">
+        <v>74</v>
       </c>
       <c r="D14" t="n">
         <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="I14" t="n">
-        <v>38</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -951,31 +882,26 @@
           <t>Laurent Changuion</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C15" t="n">
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -987,31 +913,26 @@
           <t>Chad Naude</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C16" t="n">
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H16" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1023,31 +944,26 @@
           <t>Bjorn Singh</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C17" t="n">
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1059,31 +975,26 @@
           <t>Winston Willemse</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C18" t="n">
+        <v>68</v>
       </c>
       <c r="D18" t="n">
         <v>68</v>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I18" t="n">
-        <v>32</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1095,31 +1006,26 @@
           <t>Pieter Gagiano</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C19" t="n">
+        <v>66</v>
       </c>
       <c r="D19" t="n">
         <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1131,31 +1037,26 @@
           <t>Shawn Davies</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C20" t="n">
+        <v>63</v>
       </c>
       <c r="D20" t="n">
         <v>63</v>
       </c>
       <c r="E20" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I20" t="n">
-        <v>32</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1167,30 +1068,25 @@
           <t>Dewald Van Rooyen</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C21" t="n">
+        <v>55</v>
       </c>
       <c r="D21" t="n">
         <v>55</v>
       </c>
       <c r="E21" t="n">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H21" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1203,31 +1099,26 @@
           <t>Godfrey Daniels</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C22" t="n">
+        <v>51</v>
       </c>
       <c r="D22" t="n">
         <v>51</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1239,30 +1130,25 @@
           <t>Lenny Booysen</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C23" t="n">
+        <v>45</v>
       </c>
       <c r="D23" t="n">
         <v>45</v>
       </c>
       <c r="E23" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1272,34 +1158,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>34</v>
       </c>
       <c r="D24" t="n">
         <v>34</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>34</v>
       </c>
-      <c r="F24" t="n">
-        <v>34</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1308,13 +1189,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+          <t>Fuad Adams</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>34</v>
       </c>
       <c r="D25" t="n">
         <v>34</v>
@@ -1332,9 +1211,6 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>34</v>
-      </c>
-      <c r="J25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1347,10 +1223,8 @@
           <t>Arn Smith</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C26" t="n">
+        <v>28</v>
       </c>
       <c r="D26" t="n">
         <v>28</v>
@@ -1359,7 +1233,7 @@
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1368,10 +1242,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1383,10 +1254,8 @@
           <t>Brian Plaatjies</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C27" t="n">
+        <v>24</v>
       </c>
       <c r="D27" t="n">
         <v>24</v>
@@ -1395,7 +1264,7 @@
         <v>24</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1404,9 +1273,6 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1419,30 +1285,25 @@
           <t>Kirsten Jacobs</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
+      <c r="C28" t="n">
+        <v>23</v>
       </c>
       <c r="D28" t="n">
         <v>23</v>
       </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>23</v>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1512,7 +1373,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>55</v>
+        <v>-17</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -1527,7 +1388,7 @@
         <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1540,7 +1401,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57</v>
+        <v>-15</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -1555,7 +1416,7 @@
         <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1568,7 +1429,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
         <v>17</v>
@@ -1583,7 +1444,7 @@
         <v>28</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -1596,7 +1457,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>24</v>
@@ -1611,7 +1472,7 @@
         <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1624,7 +1485,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
         <v>26</v>
@@ -1639,7 +1500,7 @@
         <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -1648,26 +1509,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Byron Labuschagne</t>
+          <t>Dale Adonis</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>64</v>
+        <v>-8</v>
       </c>
       <c r="D7" t="n">
         <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1676,26 +1537,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dale Adonis</t>
+          <t>Laurent Changuion</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>64</v>
+        <v>-6</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1704,26 +1565,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Laurent Changuion</t>
+          <t>Shaheen Boughan</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>-1</v>
       </c>
       <c r="D9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1732,26 +1593,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Shaheen Boughan</t>
+          <t>Warren Lottering</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1760,26 +1621,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Warren Lottering</t>
+          <t>Trevor Meyer</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1788,26 +1649,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trevor Meyer</t>
+          <t>Eugene Dudley</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1816,26 +1677,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ashley Spocter</t>
+          <t>Pieter Gagiano</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -1844,23 +1705,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eugene Dudley</t>
+          <t>Shawn Davies</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>-55</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
@@ -1872,23 +1733,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pieter Gagiano</t>
+          <t>John Barker</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>123</v>
+        <v>-50</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -1900,26 +1761,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shawn Davies</t>
+          <t>Chad Naude</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>-39</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1928,26 +1789,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>John Barker</t>
+          <t>Bjorn Singh</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>-33</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1956,26 +1817,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chad Naude</t>
+          <t>Winston Willemse</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>-31</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1984,26 +1845,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bjorn Singh</t>
+          <t>Godfrey Daniels</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>-9</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2012,26 +1873,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Winston Willemse</t>
+          <t>Byron Labuschagne</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2040,26 +1901,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dewald Van Rooyen</t>
+          <t>Ashley Spocter</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2068,23 +1929,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Godfrey Daniels</t>
+          <t>Ronny Kaptein</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>63</v>
+        <v>-56</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
@@ -2096,17 +1957,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lenny Booysen</t>
+          <t>Arn Smith</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74</v>
+        <v>-41</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2124,26 +1985,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ronny Kaptein</t>
+          <t>Dewald Van Rooyen</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2152,17 +2013,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fuad Adams</t>
+          <t>Lenny Booysen</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="D25" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2171,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2180,14 +2041,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Arn Smith</t>
+          <t>Fuad Adams</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -3835,4 +3696,400 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Strokes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>IPS</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>John Barker</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Arno Adonis</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ronny Kaptein</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shawn Davies</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Winston Willemse</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lucien Barnes</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Pieter Gagiano</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mika Moerat</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dale Adonis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Laurent Changuion</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shaheen Boughan</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Eugene Dudley</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Jodi Van Niekerk</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Trevor Meyer</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ranzel Louw</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bjorn Singh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Birdie Buddies</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Godfrey Daniels</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tee Tigers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Arn Smith</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Home Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chad Naude</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fairway Fighters</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Warren Lottering</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tee Stingers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>